--- a/output/pdf_financials_xlsx/FNV.xlsx
+++ b/output/pdf_financials_xlsx/FNV.xlsx
@@ -879,10 +879,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>5.323</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>1.887</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>3.9</v>
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>36.01</v>
+        <v>30.687</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>98.63800000000001</v>
+        <v>96.751</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>98.3</v>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>36.01</v>
+        <v>30.687</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>98.63800000000001</v>
+        <v>96.751</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>186.9</v>
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>23.84120867843831</v>
+        <v>20.31700001986216</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>49.38616518465113</v>
+        <v>48.44138027717696</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>82.26232394366197</v>
@@ -48718,7 +48718,7 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E565" s="5" t="n">
